--- a/data/import/FIXES/ECOLE1.xlsx
+++ b/data/import/FIXES/ECOLE1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5542C6-41FA-4DF7-B9EB-D5861F2B90FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8853B1FC-E7B4-4D8C-96E7-FF2CC29519A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>⬇  GROUP TABLE — one table per group per sheet  ⬇   Group name: "بن يحي BAC"   Sheet name = level: "BAC"</t>
   </si>
@@ -47,38 +47,23 @@
     <t>الشهر 06</t>
   </si>
   <si>
-    <t>نذير علمي</t>
-  </si>
-  <si>
-    <t>طلحي مرام</t>
-  </si>
-  <si>
-    <t>06 74 14 58 26/0674145826-</t>
-  </si>
-  <si>
-    <t>BON 14(04/08/2026)</t>
-  </si>
-  <si>
-    <t>نعيجة جيهان</t>
-  </si>
-  <si>
-    <t>06 61 15 74 25 / 06 59 23 22 15</t>
-  </si>
-  <si>
-    <t>BON 18-140(04-09/08-09/2026)</t>
-  </si>
-  <si>
-    <t>BON140 (09/09/2026)</t>
-  </si>
-  <si>
-    <t>BON321 (29/09/2026)</t>
+    <t>فوج سمية</t>
+  </si>
+  <si>
+    <t>بغالي رتاج</t>
+  </si>
+  <si>
+    <t>BON 57(03/09/2026)</t>
+  </si>
+  <si>
+    <t>BON57 (03/09/2026)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,8 +109,39 @@
       <color rgb="FF0000AA"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0000AA"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,8 +188,32 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEEFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -211,11 +251,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -231,13 +297,31 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -589,32 +673,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -644,16 +728,14 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="10"/>
+      <c r="C4" s="11">
         <v>250</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="11">
         <v>2500</v>
       </c>
       <c r="E4" s="3"/>
@@ -663,12 +745,12 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="6"/>
@@ -678,45 +760,29 @@
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3">
-        <v>250</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2500</v>
-      </c>
+      <c r="A6" s="7"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -727,7 +793,7 @@
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -738,7 +804,7 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
@@ -749,7 +815,7 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="4"/>
@@ -760,26 +826,26 @@
       <c r="I11" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -793,7 +859,7 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -804,7 +870,7 @@
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
+      <c r="A18" s="7"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -815,7 +881,7 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -826,7 +892,7 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -838,16 +904,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
